--- a/Extraction Table.xlsx
+++ b/Extraction Table.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="751" uniqueCount="318">
   <si>
     <t>A scoping review of auto-generating transformation between software development artifacts</t>
   </si>
@@ -8015,6 +8015,9 @@
       </rPr>
       <t xml:space="preserve"> (MDD Language))</t>
     </r>
+  </si>
+  <si>
+    <t>Article title: Model-Driven Development: A Tertiary Review - Journal: Sosym - author names: Raoni Sales de Oliveira, Ana Patrícia Fontes Magalhães Mascarenhas, Rita Suzana Pitangueira Maciel - Affiliation: Universidade Federal da Bahia - e-mail: raoni_si@hotmail.com</t>
   </si>
 </sst>
 </file>
@@ -8233,7 +8236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -8404,6 +8407,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -8706,7 +8712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" style="4" customWidth="1"/>
@@ -8720,3447 +8726,3454 @@
     <col min="13" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="73" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+      <c r="E1" s="73"/>
+      <c r="F1" s="73"/>
+      <c r="G1" s="73"/>
+      <c r="H1" s="73"/>
+      <c r="I1" s="73"/>
+      <c r="J1" s="73"/>
+      <c r="K1" s="73"/>
+    </row>
+    <row r="2" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A2" s="69" t="s">
         <v>302</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="B2" s="69" t="s">
         <v>312</v>
       </c>
-      <c r="C1" s="70" t="s">
+      <c r="C2" s="70" t="s">
         <v>303</v>
       </c>
-      <c r="D1" s="70" t="s">
+      <c r="D2" s="70" t="s">
         <v>304</v>
       </c>
-      <c r="E1" s="70" t="s">
+      <c r="E2" s="70" t="s">
         <v>305</v>
       </c>
-      <c r="F1" s="70" t="s">
+      <c r="F2" s="70" t="s">
         <v>306</v>
       </c>
-      <c r="G1" s="70" t="s">
+      <c r="G2" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="H1" s="70" t="s">
+      <c r="H2" s="70" t="s">
         <v>308</v>
       </c>
-      <c r="I1" s="70" t="s">
+      <c r="I2" s="70" t="s">
         <v>311</v>
       </c>
-      <c r="J1" s="70" t="s">
+      <c r="J2" s="70" t="s">
         <v>309</v>
       </c>
-      <c r="K1" s="68" t="s">
+      <c r="K2" s="68" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A2" s="15" t="s">
+    <row r="3" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A3" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B3" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F2" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H2" s="17">
+      <c r="C3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H3" s="17">
         <v>10</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I3" s="17">
         <v>23</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J3" s="33">
         <v>2017</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A3" s="9" t="s">
+    <row r="4" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A4" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B4" s="27" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G3" s="8"/>
-      <c r="H3" s="26">
+      <c r="C4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G4" s="8"/>
+      <c r="H4" s="26">
         <v>8</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I4" s="26">
         <v>16</v>
       </c>
-      <c r="J3" s="34">
+      <c r="J4" s="34">
         <v>2014</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K4" s="5" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A4" s="15" t="s">
+    <row r="5" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A5" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B5" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="17">
+      <c r="C5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="17">
         <v>10</v>
       </c>
-      <c r="I4" s="17">
+      <c r="I5" s="17">
         <v>22</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J5" s="33">
         <v>2018</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K5" s="5" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A5" s="9" t="s">
+    <row r="6" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B6" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G5" s="8"/>
-      <c r="H5" s="26">
+      <c r="C6" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="26">
         <v>8</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I6" s="26">
         <v>34</v>
       </c>
-      <c r="J5" s="34">
+      <c r="J6" s="34">
         <v>2017</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K6" s="5" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" thickBot="1">
-      <c r="A6" s="15" t="s">
+    <row r="7" spans="1:11" ht="15" customHeight="1" thickBot="1">
+      <c r="A7" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B7" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H6" s="12">
+      <c r="C7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="12">
         <v>8</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I7" s="12">
         <v>24</v>
       </c>
-      <c r="J6" s="35">
+      <c r="J7" s="35">
         <v>2017</v>
       </c>
-      <c r="K6" s="5" t="s">
+      <c r="K7" s="5" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="18" customHeight="1" thickBot="1">
-      <c r="A7" s="28" t="s">
+    <row r="8" spans="1:11" ht="18" customHeight="1" thickBot="1">
+      <c r="A8" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B8" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="26">
+      <c r="C8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="26">
         <v>8</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I8" s="26">
         <v>59</v>
       </c>
-      <c r="J7" s="34">
+      <c r="J8" s="34">
         <v>2017</v>
       </c>
-      <c r="K7" s="5" t="s">
+      <c r="K8" s="5" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A8" s="15" t="s">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A9" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B9" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H8" s="17">
+      <c r="C9" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H9" s="17">
         <v>10</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I9" s="17">
         <v>134</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J9" s="33">
         <v>2014</v>
       </c>
-      <c r="K8" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A9" s="9" t="s">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A10" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B9" s="25" t="s">
+      <c r="B10" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="26">
+      <c r="C10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G10" s="8"/>
+      <c r="H10" s="26">
         <v>8</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I10" s="26">
         <v>25</v>
       </c>
-      <c r="J9" s="34">
+      <c r="J10" s="34">
         <v>2017</v>
       </c>
-      <c r="K9" s="5" t="s">
+      <c r="K10" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A10" s="51" t="s">
+    <row r="11" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A11" s="51" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B11" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="17">
+      <c r="C11" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="17">
         <v>8</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I11" s="17">
         <v>123</v>
       </c>
-      <c r="J10" s="33">
+      <c r="J11" s="33">
         <v>2020</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K11" s="5" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A11" s="52" t="s">
+    <row r="12" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A12" s="52" t="s">
         <v>98</v>
       </c>
-      <c r="B11" s="25" t="s">
+      <c r="B12" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="26">
+      <c r="C12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G12" s="8"/>
+      <c r="H12" s="26">
         <v>8</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I12" s="26">
         <v>19</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J12" s="34">
         <v>2018</v>
       </c>
-      <c r="K11" s="5" t="s">
+      <c r="K12" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A12" s="35" t="s">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A13" s="35" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B13" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="17">
+      <c r="C13" s="11"/>
+      <c r="D13" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="17">
         <v>6</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I13" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J13" s="33">
         <v>2018</v>
       </c>
-      <c r="K12" s="5" t="s">
+      <c r="K13" s="5" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="17.25" customHeight="1" thickBot="1">
-      <c r="A13" s="28" t="s">
+    <row r="14" spans="1:11" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A14" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="B13" s="25" t="s">
+      <c r="B14" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="C13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="H13" s="26">
+      <c r="C14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="26">
         <v>10</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I14" s="26">
         <v>48</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J14" s="34">
         <v>2018</v>
       </c>
-      <c r="K13" s="5" t="s">
+      <c r="K14" s="5" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A14" s="35" t="s">
+    <row r="15" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A15" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B15" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14" s="11"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="17">
+      <c r="C15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="17">
         <v>6</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I15" s="17">
         <v>54</v>
       </c>
-      <c r="J14" s="33">
+      <c r="J15" s="33">
         <v>2021</v>
       </c>
-      <c r="K14" s="5" t="s">
+      <c r="K15" s="5" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A15" s="9" t="s">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A16" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="25" t="s">
+      <c r="B16" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="C15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="H15" s="26">
+      <c r="C16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="26">
         <v>10</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I16" s="26">
         <v>56</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J16" s="34">
         <v>2019</v>
       </c>
-      <c r="K15" s="5" t="s">
+      <c r="K16" s="5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="15.75" thickBot="1">
-      <c r="A16" s="35" t="s">
+    <row r="17" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A17" s="35" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B17" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="61" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="17">
+      <c r="C17" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="E17" s="61" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="17">
         <v>6</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I17" s="17">
         <v>415</v>
       </c>
-      <c r="J16" s="33">
+      <c r="J17" s="33">
         <v>2021</v>
       </c>
-      <c r="K16" s="5" t="s">
+      <c r="K17" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="M16" s="2"/>
+      <c r="M17" s="2"/>
     </row>
-    <row r="17" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A17" s="28" t="s">
+    <row r="18" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A18" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B18" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="8"/>
-      <c r="H17" s="26">
+      <c r="C18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" s="8"/>
+      <c r="H18" s="26">
         <v>8</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I18" s="26">
         <v>390</v>
       </c>
-      <c r="J17" s="34">
+      <c r="J18" s="34">
         <v>2016</v>
       </c>
-      <c r="K17" s="5" t="s">
+      <c r="K18" s="5" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A18" s="15" t="s">
+    <row r="19" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A19" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B19" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="H18" s="17">
+      <c r="C19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="17">
         <v>10</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I19" s="17">
         <v>10</v>
       </c>
-      <c r="J18" s="33">
+      <c r="J19" s="33">
         <v>2022</v>
       </c>
-      <c r="K18" s="5" t="s">
+      <c r="K19" s="5" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A19" s="28" t="s">
+    <row r="20" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A20" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B20" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C19" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="G19" s="40"/>
-      <c r="H19" s="39">
+      <c r="C20" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="40"/>
+      <c r="H20" s="39">
         <v>8</v>
       </c>
-      <c r="I19" s="39">
+      <c r="I20" s="39">
         <v>84</v>
       </c>
-      <c r="J19" s="41">
+      <c r="J20" s="41">
         <v>2022</v>
       </c>
-      <c r="K19" s="71" t="s">
+      <c r="K20" s="71" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A20" s="15" t="s">
+    <row r="21" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A21" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B21" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="17">
+      <c r="C21" s="11"/>
+      <c r="D21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G21" s="11"/>
+      <c r="H21" s="17">
         <v>6</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I21" s="17">
         <v>61</v>
       </c>
-      <c r="J20" s="33">
+      <c r="J21" s="33">
         <v>2015</v>
       </c>
-      <c r="K20" s="5" t="s">
+      <c r="K21" s="5" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A21" s="9" t="s">
+    <row r="22" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A22" s="9" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B22" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="26">
+      <c r="C22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G22" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="26">
         <v>10</v>
       </c>
-      <c r="I21" s="26">
+      <c r="I22" s="26">
         <v>12</v>
       </c>
-      <c r="J21" s="34">
+      <c r="J22" s="34">
         <v>2014</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K22" s="5" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A22" s="51" t="s">
+    <row r="23" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A23" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B23" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="17">
+      <c r="C23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="17">
         <v>8</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I23" s="17">
         <v>38</v>
       </c>
-      <c r="J22" s="33">
+      <c r="J23" s="33">
         <v>2016</v>
       </c>
-      <c r="K22" s="5" t="s">
+      <c r="K23" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A23" s="9" t="s">
+    <row r="24" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A24" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B24" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="D23" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="E23" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="F23" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="H23" s="39">
+      <c r="C24" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="G24" s="62" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" s="39">
         <v>10</v>
       </c>
-      <c r="I23" s="39">
+      <c r="I24" s="39">
         <v>58</v>
       </c>
-      <c r="J23" s="41">
+      <c r="J24" s="41">
         <v>2024</v>
       </c>
-      <c r="K23" s="5" t="s">
+      <c r="K24" s="5" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A24" s="15" t="s">
+    <row r="25" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A25" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B25" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="17">
+      <c r="C25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G25" s="11"/>
+      <c r="H25" s="17">
         <v>8</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I25" s="17">
         <v>27</v>
       </c>
-      <c r="J24" s="33">
+      <c r="J25" s="33">
         <v>2020</v>
       </c>
-      <c r="K24" s="5" t="s">
+      <c r="K25" s="5" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A25" s="9" t="s">
+    <row r="26" spans="1:13" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A26" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B25" s="25" t="s">
+      <c r="B26" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="C25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="H25" s="26">
+      <c r="C26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" s="26">
         <v>10</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I26" s="26">
         <v>36</v>
       </c>
-      <c r="J25" s="34">
+      <c r="J26" s="34">
         <v>2020</v>
       </c>
-      <c r="K25" s="5" t="s">
+      <c r="K26" s="5" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A26" s="53" t="s">
+    <row r="27" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A27" s="53" t="s">
         <v>99</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B27" s="16" t="s">
         <v>109</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F26" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G26" s="11"/>
-      <c r="H26" s="17">
+      <c r="C27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G27" s="11"/>
+      <c r="H27" s="17">
         <v>8</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I27" s="17">
         <v>893</v>
       </c>
-      <c r="J26" s="33">
+      <c r="J27" s="33">
         <v>2015</v>
       </c>
-      <c r="K26" s="5" t="s">
+      <c r="K27" s="5" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A27" s="10" t="s">
+    <row r="28" spans="1:13" ht="15.75" thickBot="1">
+      <c r="A28" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B27" s="25" t="s">
+      <c r="B28" s="25" t="s">
         <v>148</v>
       </c>
-      <c r="C27" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="E27" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="F27" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="G27" s="8"/>
-      <c r="H27" s="26">
+      <c r="C28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="8"/>
+      <c r="H28" s="26">
         <v>8</v>
       </c>
-      <c r="I27" s="26">
+      <c r="I28" s="26">
         <v>40</v>
       </c>
-      <c r="J27" s="34">
+      <c r="J28" s="34">
         <v>2019</v>
       </c>
-      <c r="K27" s="5" t="s">
+      <c r="K28" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
-      <c r="A28" s="20" t="s">
+    <row r="29" spans="1:13">
+      <c r="A29" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B29" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="C28" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D28" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="12">
+      <c r="C29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G29" s="23"/>
+      <c r="H29" s="12">
         <v>8</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I29" s="12">
         <v>289</v>
       </c>
-      <c r="J28" s="35">
+      <c r="J29" s="35">
         <v>2015</v>
       </c>
-      <c r="K28" s="5" t="s">
+      <c r="K29" s="5" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
-      <c r="A29" s="32" t="s">
+    <row r="30" spans="1:13">
+      <c r="A30" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B30" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="C29" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D29" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F29" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G29" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H29" s="29">
+      <c r="C30" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G30" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H30" s="29">
         <v>10</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I30" s="29">
         <v>64</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J30" s="28">
         <v>2019</v>
       </c>
-      <c r="K29" s="5" t="s">
+      <c r="K30" s="5" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
-      <c r="A30" s="51" t="s">
+    <row r="31" spans="1:13">
+      <c r="A31" s="51" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B31" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D30" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="12">
+      <c r="C31" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G31" s="23"/>
+      <c r="H31" s="12">
         <v>8</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I31" s="12">
         <v>212</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J31" s="35">
         <v>2017</v>
       </c>
-      <c r="K30" s="5" t="s">
+      <c r="K31" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
-      <c r="A31" s="28" t="s">
+    <row r="32" spans="1:13">
+      <c r="A32" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="50" t="s">
+      <c r="B32" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D31" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E31" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F31" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G31" s="43"/>
-      <c r="H31" s="42">
+      <c r="C32" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D32" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F32" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32" s="43"/>
+      <c r="H32" s="42">
         <v>8</v>
       </c>
-      <c r="I31" s="42">
+      <c r="I32" s="42">
         <v>30</v>
       </c>
-      <c r="J31" s="44">
+      <c r="J32" s="44">
         <v>2025</v>
       </c>
-      <c r="K31" s="5" t="s">
+      <c r="K32" s="5" t="s">
         <v>262</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="C32" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H32" s="12">
-        <v>10</v>
-      </c>
-      <c r="I32" s="12">
-        <v>37</v>
-      </c>
-      <c r="J32" s="35">
-        <v>2022</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G33" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H33" s="29">
-        <v>6</v>
-      </c>
-      <c r="I33" s="29">
-        <v>30</v>
-      </c>
-      <c r="J33" s="28">
-        <v>2018</v>
+      <c r="A33" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="C33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H33" s="12">
+        <v>10</v>
+      </c>
+      <c r="I33" s="12">
+        <v>37</v>
+      </c>
+      <c r="J33" s="35">
+        <v>2022</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E34" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="12">
+      <c r="A34" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="31"/>
+      <c r="F34" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G34" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H34" s="29">
         <v>6</v>
       </c>
-      <c r="I34" s="12">
-        <v>8</v>
-      </c>
-      <c r="J34" s="35">
-        <v>2016</v>
+      <c r="I34" s="29">
+        <v>30</v>
+      </c>
+      <c r="J34" s="28">
+        <v>2018</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="9" t="s">
-        <v>156</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="C35" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E35" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F35" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G35" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H35" s="29">
-        <v>10</v>
-      </c>
-      <c r="I35" s="29">
-        <v>32</v>
-      </c>
-      <c r="J35" s="28">
-        <v>2022</v>
+      <c r="A35" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F35" s="23"/>
+      <c r="G35" s="23"/>
+      <c r="H35" s="12">
+        <v>6</v>
+      </c>
+      <c r="I35" s="12">
+        <v>8</v>
+      </c>
+      <c r="J35" s="35">
+        <v>2016</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D36" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="12">
-        <v>8</v>
-      </c>
-      <c r="I36" s="12">
-        <v>80</v>
-      </c>
-      <c r="J36" s="35">
+      <c r="A36" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D36" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F36" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G36" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="29">
+        <v>10</v>
+      </c>
+      <c r="I36" s="29">
+        <v>32</v>
+      </c>
+      <c r="J36" s="28">
         <v>2022</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>276</v>
+        <v>227</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="9" t="s">
-        <v>160</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D37" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F37" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G37" s="31"/>
-      <c r="H37" s="29">
+      <c r="A37" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G37" s="23"/>
+      <c r="H37" s="12">
         <v>8</v>
       </c>
-      <c r="I37" s="29">
-        <v>143</v>
-      </c>
-      <c r="J37" s="28">
+      <c r="I37" s="12">
+        <v>80</v>
+      </c>
+      <c r="J37" s="35">
         <v>2022</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D38" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G38" s="23"/>
-      <c r="H38" s="12">
+      <c r="A38" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D38" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F38" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G38" s="31"/>
+      <c r="H38" s="29">
         <v>8</v>
       </c>
-      <c r="I38" s="12">
-        <v>140</v>
-      </c>
-      <c r="J38" s="35">
-        <v>2021</v>
+      <c r="I38" s="29">
+        <v>143</v>
+      </c>
+      <c r="J38" s="28">
+        <v>2022</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>293</v>
+        <v>277</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="9" t="s">
-        <v>164</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F39" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G39" s="31"/>
-      <c r="H39" s="29">
-        <v>6</v>
-      </c>
-      <c r="I39" s="29">
-        <v>35</v>
-      </c>
-      <c r="J39" s="28">
-        <v>2019</v>
+      <c r="A39" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G39" s="23"/>
+      <c r="H39" s="12">
+        <v>8</v>
+      </c>
+      <c r="I39" s="12">
+        <v>140</v>
+      </c>
+      <c r="J39" s="35">
+        <v>2021</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="C40" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D40" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F40" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G40" s="23"/>
-      <c r="H40" s="12">
-        <v>8</v>
-      </c>
-      <c r="I40" s="12">
-        <v>51</v>
-      </c>
-      <c r="J40" s="35">
-        <v>2017</v>
+      <c r="A40" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F40" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" s="31"/>
+      <c r="H40" s="29">
+        <v>6</v>
+      </c>
+      <c r="I40" s="29">
+        <v>35</v>
+      </c>
+      <c r="J40" s="28">
+        <v>2019</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>221</v>
+        <v>278</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D41" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E41" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F41" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G41" s="31"/>
-      <c r="H41" s="29">
+      <c r="A41" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G41" s="23"/>
+      <c r="H41" s="12">
         <v>8</v>
       </c>
-      <c r="I41" s="29">
-        <v>97</v>
-      </c>
-      <c r="J41" s="28">
-        <v>2020</v>
+      <c r="I41" s="12">
+        <v>51</v>
+      </c>
+      <c r="J41" s="35">
+        <v>2017</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G42" s="23"/>
-      <c r="H42" s="12">
+      <c r="A42" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D42" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G42" s="31"/>
+      <c r="H42" s="29">
         <v>8</v>
       </c>
-      <c r="I42" s="12">
-        <v>408</v>
-      </c>
-      <c r="J42" s="35">
+      <c r="I42" s="29">
+        <v>97</v>
+      </c>
+      <c r="J42" s="28">
         <v>2020</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="28" t="s">
-        <v>35</v>
-      </c>
-      <c r="B43" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C43" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E43" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F43" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G43" s="43"/>
-      <c r="H43" s="42">
+      <c r="A43" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="C43" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G43" s="23"/>
+      <c r="H43" s="12">
         <v>8</v>
       </c>
-      <c r="I43" s="42">
-        <v>43</v>
-      </c>
-      <c r="J43" s="44">
-        <v>2023</v>
-      </c>
-      <c r="K43" s="13" t="s">
-        <v>299</v>
+      <c r="I43" s="12">
+        <v>408</v>
+      </c>
+      <c r="J43" s="35">
+        <v>2020</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D44" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G44" s="23"/>
-      <c r="H44" s="12">
+      <c r="A44" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" s="43"/>
+      <c r="H44" s="42">
         <v>8</v>
       </c>
-      <c r="I44" s="12">
-        <v>25</v>
-      </c>
-      <c r="J44" s="35">
-        <v>2015</v>
-      </c>
-      <c r="K44" s="5" t="s">
-        <v>219</v>
+      <c r="I44" s="42">
+        <v>43</v>
+      </c>
+      <c r="J44" s="44">
+        <v>2023</v>
+      </c>
+      <c r="K44" s="13" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="50" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="D45" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="E45" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="F45" s="49" t="s">
-        <v>118</v>
-      </c>
-      <c r="G45" s="49"/>
-      <c r="H45" s="42">
+      <c r="A45" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C45" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G45" s="23"/>
+      <c r="H45" s="12">
         <v>8</v>
       </c>
-      <c r="I45" s="42">
-        <v>34</v>
-      </c>
-      <c r="J45" s="44">
-        <v>2024</v>
+      <c r="I45" s="12">
+        <v>25</v>
+      </c>
+      <c r="J45" s="35">
+        <v>2015</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>263</v>
+        <v>219</v>
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="15" t="s">
-        <v>172</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>173</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D46" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F46" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G46" s="23"/>
-      <c r="H46" s="12">
+      <c r="A46" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46" s="50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C46" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D46" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="E46" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="F46" s="49" t="s">
+        <v>118</v>
+      </c>
+      <c r="G46" s="49"/>
+      <c r="H46" s="42">
         <v>8</v>
       </c>
-      <c r="I46" s="12">
-        <v>36</v>
-      </c>
-      <c r="J46" s="35">
-        <v>2022</v>
+      <c r="I46" s="42">
+        <v>34</v>
+      </c>
+      <c r="J46" s="44">
+        <v>2024</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>234</v>
+        <v>263</v>
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C47" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E47" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G47" s="31"/>
-      <c r="H47" s="29">
+      <c r="A47" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G47" s="23"/>
+      <c r="H47" s="12">
         <v>8</v>
       </c>
-      <c r="I47" s="29">
-        <v>31</v>
-      </c>
-      <c r="J47" s="28">
-        <v>2018</v>
+      <c r="I47" s="12">
+        <v>36</v>
+      </c>
+      <c r="J47" s="35">
+        <v>2022</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>206</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" spans="1:12">
-      <c r="A48" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B48" s="58" t="s">
-        <v>23</v>
-      </c>
-      <c r="C48" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D48" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E48" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F48" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G48" s="47"/>
-      <c r="H48" s="46">
+      <c r="A48" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D48" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E48" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F48" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G48" s="31"/>
+      <c r="H48" s="29">
         <v>8</v>
       </c>
-      <c r="I48" s="46">
-        <v>6500</v>
-      </c>
-      <c r="J48" s="48">
-        <v>2023</v>
-      </c>
-      <c r="K48" s="71" t="s">
-        <v>314</v>
+      <c r="I48" s="29">
+        <v>31</v>
+      </c>
+      <c r="J48" s="28">
+        <v>2018</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="L48" s="4" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="49" spans="1:11">
-      <c r="A49" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="50" t="s">
-        <v>10</v>
-      </c>
-      <c r="C49" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D49" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F49" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G49" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="H49" s="42">
-        <v>10</v>
-      </c>
-      <c r="I49" s="42">
-        <v>104</v>
-      </c>
-      <c r="J49" s="44">
-        <v>2025</v>
-      </c>
-      <c r="K49" s="14" t="s">
-        <v>298</v>
+      <c r="A49" s="35" t="s">
+        <v>37</v>
+      </c>
+      <c r="B49" s="58" t="s">
+        <v>23</v>
+      </c>
+      <c r="C49" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F49" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G49" s="47"/>
+      <c r="H49" s="46">
+        <v>8</v>
+      </c>
+      <c r="I49" s="46">
+        <v>6500</v>
+      </c>
+      <c r="J49" s="48">
+        <v>2023</v>
+      </c>
+      <c r="K49" s="71" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:11">
-      <c r="A50" s="51" t="s">
-        <v>82</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D50" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H50" s="12">
+      <c r="A50" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="I50" s="12">
-        <v>42</v>
-      </c>
-      <c r="J50" s="35">
-        <v>2018</v>
-      </c>
-      <c r="K50" s="5" t="s">
-        <v>223</v>
+      <c r="C50" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D50" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E50" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F50" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G50" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="H50" s="42">
+        <v>10</v>
+      </c>
+      <c r="I50" s="42">
+        <v>104</v>
+      </c>
+      <c r="J50" s="44">
+        <v>2025</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="51" spans="1:11">
-      <c r="A51" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C51" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D51" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E51" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F51" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G51" s="31"/>
-      <c r="H51" s="29">
-        <v>8</v>
-      </c>
-      <c r="I51" s="29">
-        <v>15</v>
-      </c>
-      <c r="J51" s="28">
-        <v>2021</v>
+      <c r="A51" s="51" t="s">
+        <v>82</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H51" s="12">
+        <v>10</v>
+      </c>
+      <c r="I51" s="12">
+        <v>42</v>
+      </c>
+      <c r="J51" s="35">
+        <v>2018</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="52" spans="1:11">
-      <c r="A52" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D52" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F52" s="23"/>
-      <c r="G52" s="23"/>
-      <c r="H52" s="12">
-        <v>6</v>
-      </c>
-      <c r="I52" s="12">
-        <v>19</v>
-      </c>
-      <c r="J52" s="35">
-        <v>2019</v>
+      <c r="A52" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="C52" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E52" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G52" s="31"/>
+      <c r="H52" s="29">
+        <v>8</v>
+      </c>
+      <c r="I52" s="29">
+        <v>15</v>
+      </c>
+      <c r="J52" s="28">
+        <v>2021</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>280</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:11">
-      <c r="A53" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="B53" s="50" t="s">
-        <v>4</v>
-      </c>
-      <c r="C53" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D53" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E53" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F53" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G53" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="H53" s="42">
-        <v>10</v>
-      </c>
-      <c r="I53" s="42">
-        <v>24</v>
-      </c>
-      <c r="J53" s="44">
-        <v>2024</v>
+      <c r="A53" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F53" s="23"/>
+      <c r="G53" s="23"/>
+      <c r="H53" s="12">
+        <v>6</v>
+      </c>
+      <c r="I53" s="12">
+        <v>19</v>
+      </c>
+      <c r="J53" s="35">
+        <v>2019</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
     </row>
     <row r="54" spans="1:11">
-      <c r="A54" s="15" t="s">
-        <v>178</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>179</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H54" s="12">
+      <c r="A54" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D54" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G54" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="H54" s="42">
         <v>10</v>
       </c>
-      <c r="I54" s="12">
-        <v>4</v>
-      </c>
-      <c r="J54" s="67">
-        <v>2017</v>
+      <c r="I54" s="42">
+        <v>24</v>
+      </c>
+      <c r="J54" s="44">
+        <v>2024</v>
       </c>
       <c r="K54" s="5" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
     </row>
     <row r="55" spans="1:11">
-      <c r="A55" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="30" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E55" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F55" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G55" s="31"/>
-      <c r="H55" s="29">
-        <v>8</v>
-      </c>
-      <c r="I55" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="J55" s="66">
-        <v>2016</v>
+      <c r="A55" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D55" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E55" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H55" s="12">
+        <v>10</v>
+      </c>
+      <c r="I55" s="12">
+        <v>4</v>
+      </c>
+      <c r="J55" s="67">
+        <v>2017</v>
       </c>
       <c r="K55" s="5" t="s">
-        <v>281</v>
+        <v>243</v>
       </c>
     </row>
     <row r="56" spans="1:11">
-      <c r="A56" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="B56" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="C56" s="23"/>
-      <c r="D56" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G56" s="23"/>
-      <c r="H56" s="12">
-        <v>6</v>
-      </c>
-      <c r="I56" s="12">
-        <v>82</v>
-      </c>
-      <c r="J56" s="35">
+      <c r="A56" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="30" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G56" s="31"/>
+      <c r="H56" s="29">
+        <v>8</v>
+      </c>
+      <c r="I56" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="J56" s="66">
         <v>2016</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
     </row>
     <row r="57" spans="1:11">
-      <c r="A57" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="C57" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E57" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F57" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G57" s="31"/>
-      <c r="H57" s="29">
-        <v>8</v>
-      </c>
-      <c r="I57" s="29">
-        <v>481</v>
-      </c>
-      <c r="J57" s="28">
-        <v>2018</v>
+      <c r="A57" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>112</v>
+      </c>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G57" s="23"/>
+      <c r="H57" s="12">
+        <v>6</v>
+      </c>
+      <c r="I57" s="12">
+        <v>82</v>
+      </c>
+      <c r="J57" s="35">
+        <v>2016</v>
       </c>
       <c r="K57" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="58" spans="1:11">
-      <c r="A58" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="B58" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F58" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G58" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H58" s="12">
-        <v>10</v>
-      </c>
-      <c r="I58" s="12">
-        <v>230</v>
-      </c>
-      <c r="J58" s="35">
-        <v>2020</v>
+      <c r="A58" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D58" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E58" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F58" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G58" s="31"/>
+      <c r="H58" s="29">
+        <v>8</v>
+      </c>
+      <c r="I58" s="29">
+        <v>481</v>
+      </c>
+      <c r="J58" s="28">
+        <v>2018</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
     </row>
     <row r="59" spans="1:11">
-      <c r="A59" s="54" t="s">
-        <v>63</v>
-      </c>
-      <c r="B59" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C59" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D59" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E59" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F59" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G59" s="31"/>
-      <c r="H59" s="29">
-        <v>8</v>
-      </c>
-      <c r="I59" s="29">
-        <v>119</v>
-      </c>
-      <c r="J59" s="28">
+      <c r="A59" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="B59" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H59" s="12">
+        <v>10</v>
+      </c>
+      <c r="I59" s="12">
+        <v>230</v>
+      </c>
+      <c r="J59" s="35">
         <v>2020</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>211</v>
+        <v>236</v>
       </c>
     </row>
     <row r="60" spans="1:11">
-      <c r="A60" s="53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B60" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="C60" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D60" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E60" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G60" s="23"/>
-      <c r="H60" s="12">
+      <c r="A60" s="54" t="s">
+        <v>63</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C60" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D60" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E60" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G60" s="31"/>
+      <c r="H60" s="29">
         <v>8</v>
       </c>
-      <c r="I60" s="12">
-        <v>70</v>
-      </c>
-      <c r="J60" s="35">
-        <v>2015</v>
+      <c r="I60" s="29">
+        <v>119</v>
+      </c>
+      <c r="J60" s="28">
+        <v>2020</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
     </row>
     <row r="61" spans="1:11">
-      <c r="A61" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B61" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C61" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D61" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E61" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F61" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G61" s="31"/>
-      <c r="H61" s="29">
+      <c r="A61" s="53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>113</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D61" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G61" s="23"/>
+      <c r="H61" s="12">
         <v>8</v>
       </c>
-      <c r="I61" s="29">
-        <v>15</v>
-      </c>
-      <c r="J61" s="28">
-        <v>2017</v>
+      <c r="I61" s="12">
+        <v>70</v>
+      </c>
+      <c r="J61" s="35">
+        <v>2015</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:11">
-      <c r="A62" s="20" t="s">
-        <v>186</v>
-      </c>
-      <c r="B62" s="20" t="s">
-        <v>187</v>
-      </c>
-      <c r="C62" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D62" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E62" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F62" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G62" s="23"/>
-      <c r="H62" s="12">
+      <c r="A62" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="B62" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D62" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F62" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G62" s="31"/>
+      <c r="H62" s="29">
         <v>8</v>
       </c>
-      <c r="I62" s="12">
-        <v>53</v>
-      </c>
-      <c r="J62" s="35">
-        <v>2022</v>
+      <c r="I62" s="29">
+        <v>15</v>
+      </c>
+      <c r="J62" s="28">
+        <v>2017</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>282</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:11">
-      <c r="A63" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="B63" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="C63" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D63" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E63" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F63" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G63" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H63" s="29">
-        <v>10</v>
-      </c>
-      <c r="I63" s="29">
-        <v>94</v>
-      </c>
-      <c r="J63" s="28">
-        <v>2015</v>
+      <c r="A63" s="20" t="s">
+        <v>186</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G63" s="23"/>
+      <c r="H63" s="12">
+        <v>8</v>
+      </c>
+      <c r="I63" s="12">
+        <v>53</v>
+      </c>
+      <c r="J63" s="35">
+        <v>2022</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>244</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:11">
-      <c r="A64" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="B64" s="59" t="s">
-        <v>17</v>
-      </c>
-      <c r="C64" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="D64" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="E64" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="F64" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="G64" s="63"/>
-      <c r="H64" s="46">
-        <v>8</v>
-      </c>
-      <c r="I64" s="46">
-        <v>37</v>
-      </c>
-      <c r="J64" s="48">
-        <v>2023</v>
+      <c r="A64" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="C64" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D64" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E64" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F64" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G64" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H64" s="29">
+        <v>10</v>
+      </c>
+      <c r="I64" s="29">
+        <v>94</v>
+      </c>
+      <c r="J64" s="28">
+        <v>2015</v>
       </c>
       <c r="K64" s="5" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" spans="1:13">
-      <c r="A65" s="55" t="s">
-        <v>104</v>
-      </c>
-      <c r="B65" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="C65" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D65" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E65" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F65" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G65" s="31"/>
-      <c r="H65" s="29">
+      <c r="A65" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="B65" s="59" t="s">
+        <v>17</v>
+      </c>
+      <c r="C65" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="E65" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="F65" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G65" s="63"/>
+      <c r="H65" s="46">
         <v>8</v>
       </c>
-      <c r="I65" s="29">
-        <v>4859</v>
-      </c>
-      <c r="J65" s="28">
-        <v>2018</v>
+      <c r="I65" s="46">
+        <v>37</v>
+      </c>
+      <c r="J65" s="48">
+        <v>2023</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>247</v>
+        <v>300</v>
       </c>
     </row>
     <row r="66" spans="1:13">
-      <c r="A66" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="B66" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E66" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F66" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G66" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H66" s="12">
-        <v>10</v>
-      </c>
-      <c r="I66" s="12">
-        <v>12</v>
-      </c>
-      <c r="J66" s="35">
-        <v>2017</v>
+      <c r="A66" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C66" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D66" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E66" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F66" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G66" s="31"/>
+      <c r="H66" s="29">
+        <v>8</v>
+      </c>
+      <c r="I66" s="29">
+        <v>4859</v>
+      </c>
+      <c r="J66" s="28">
+        <v>2018</v>
       </c>
       <c r="K66" s="5" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="67" spans="1:13">
-      <c r="A67" s="32" t="s">
-        <v>42</v>
-      </c>
-      <c r="B67" s="60" t="s">
-        <v>14</v>
-      </c>
-      <c r="C67" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="D67" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E67" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="F67" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="G67" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="H67" s="42">
+      <c r="A67" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="B67" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H67" s="12">
         <v>10</v>
       </c>
-      <c r="I67" s="42">
-        <v>98</v>
-      </c>
-      <c r="J67" s="44">
-        <v>2024</v>
+      <c r="I67" s="12">
+        <v>12</v>
+      </c>
+      <c r="J67" s="35">
+        <v>2017</v>
       </c>
       <c r="K67" s="5" t="s">
-        <v>265</v>
+        <v>237</v>
       </c>
     </row>
     <row r="68" spans="1:13">
-      <c r="A68" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="59" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="D68" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="E68" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="F68" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="G68" s="63"/>
-      <c r="H68" s="46">
-        <v>8</v>
-      </c>
-      <c r="I68" s="46">
-        <v>52</v>
-      </c>
-      <c r="J68" s="48">
-        <v>2025</v>
+      <c r="A68" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B68" s="60" t="s">
+        <v>14</v>
+      </c>
+      <c r="C68" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D68" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="E68" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F68" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="G68" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="H68" s="42">
+        <v>10</v>
+      </c>
+      <c r="I68" s="42">
+        <v>98</v>
+      </c>
+      <c r="J68" s="44">
+        <v>2024</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="M68" s="3"/>
+        <v>265</v>
+      </c>
     </row>
     <row r="69" spans="1:13">
-      <c r="A69" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B69" s="60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E69" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F69" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G69" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="H69" s="42">
-        <v>10</v>
-      </c>
-      <c r="I69" s="42">
-        <v>20</v>
-      </c>
-      <c r="J69" s="44">
-        <v>2023</v>
-      </c>
-      <c r="K69" s="71" t="s">
-        <v>315</v>
-      </c>
+      <c r="A69" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="59" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D69" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="E69" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="F69" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G69" s="63"/>
+      <c r="H69" s="46">
+        <v>8</v>
+      </c>
+      <c r="I69" s="46">
+        <v>52</v>
+      </c>
+      <c r="J69" s="48">
+        <v>2025</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="M69" s="3"/>
     </row>
     <row r="70" spans="1:13">
-      <c r="A70" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="B70" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C70" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D70" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G70" s="23"/>
-      <c r="H70" s="12">
-        <v>8</v>
-      </c>
-      <c r="I70" s="12">
-        <v>28</v>
-      </c>
-      <c r="J70" s="21">
-        <v>2015</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>251</v>
+      <c r="A70" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" s="60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D70" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E70" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F70" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G70" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="H70" s="42">
+        <v>10</v>
+      </c>
+      <c r="I70" s="42">
+        <v>20</v>
+      </c>
+      <c r="J70" s="44">
+        <v>2023</v>
+      </c>
+      <c r="K70" s="71" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="1:13">
-      <c r="A71" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="B71" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="C71" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="D71" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E71" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="F71" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="G71" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="H71" s="45">
-        <v>10</v>
-      </c>
-      <c r="I71" s="45">
-        <v>21</v>
-      </c>
-      <c r="J71" s="50">
-        <v>2023</v>
-      </c>
-      <c r="K71" s="72" t="s">
-        <v>316</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>44</v>
+      <c r="A71" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E71" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F71" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G71" s="23"/>
+      <c r="H71" s="12">
+        <v>8</v>
+      </c>
+      <c r="I71" s="12">
+        <v>28</v>
+      </c>
+      <c r="J71" s="21">
+        <v>2015</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="72" spans="1:13">
-      <c r="A72" s="53" t="s">
-        <v>81</v>
-      </c>
-      <c r="B72" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D72" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E72" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H72" s="12">
-        <v>8</v>
-      </c>
-      <c r="I72" s="12">
-        <v>13</v>
-      </c>
-      <c r="J72" s="35">
-        <v>2014</v>
-      </c>
-      <c r="K72" s="5" t="s">
-        <v>225</v>
+      <c r="A72" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D72" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="E72" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F72" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="G72" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="H72" s="45">
+        <v>10</v>
+      </c>
+      <c r="I72" s="45">
+        <v>21</v>
+      </c>
+      <c r="J72" s="50">
+        <v>2023</v>
+      </c>
+      <c r="K72" s="72" t="s">
+        <v>316</v>
+      </c>
+      <c r="L72" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="73" spans="1:13">
-      <c r="A73" s="55" t="s">
-        <v>64</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C73" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D73" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E73" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F73" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H73" s="29">
-        <v>10</v>
-      </c>
-      <c r="I73" s="29">
-        <v>48</v>
-      </c>
-      <c r="J73" s="28">
+      <c r="A73" s="53" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D73" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F73" s="23"/>
+      <c r="G73" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H73" s="12">
+        <v>8</v>
+      </c>
+      <c r="I73" s="12">
+        <v>13</v>
+      </c>
+      <c r="J73" s="35">
         <v>2014</v>
       </c>
       <c r="K73" s="5" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
     </row>
     <row r="74" spans="1:13">
-      <c r="A74" s="20" t="s">
-        <v>194</v>
-      </c>
-      <c r="B74" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="C74" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D74" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E74" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F74" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G74" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H74" s="12">
+      <c r="A74" s="55" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C74" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D74" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E74" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F74" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H74" s="29">
         <v>10</v>
       </c>
-      <c r="I74" s="12">
-        <v>82</v>
-      </c>
-      <c r="J74" s="35">
-        <v>2019</v>
+      <c r="I74" s="29">
+        <v>48</v>
+      </c>
+      <c r="J74" s="28">
+        <v>2014</v>
       </c>
       <c r="K74" s="5" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
     </row>
     <row r="75" spans="1:13">
-      <c r="A75" s="10" t="s">
-        <v>196</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>197</v>
-      </c>
-      <c r="C75" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D75" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E75" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F75" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G75" s="31"/>
-      <c r="H75" s="29">
-        <v>8</v>
-      </c>
-      <c r="I75" s="29">
-        <v>129</v>
-      </c>
-      <c r="J75" s="28">
-        <v>2015</v>
+      <c r="A75" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="B75" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D75" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E75" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H75" s="12">
+        <v>10</v>
+      </c>
+      <c r="I75" s="12">
+        <v>82</v>
+      </c>
+      <c r="J75" s="35">
+        <v>2019</v>
       </c>
       <c r="K75" s="5" t="s">
-        <v>283</v>
+        <v>248</v>
       </c>
     </row>
     <row r="76" spans="1:13">
-      <c r="A76" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="B76" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="C76" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D76" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E76" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F76" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G76" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="H76" s="12">
-        <v>10</v>
-      </c>
-      <c r="I76" s="12">
-        <v>23</v>
-      </c>
-      <c r="J76" s="35">
-        <v>2020</v>
+      <c r="A76" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="C76" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D76" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G76" s="31"/>
+      <c r="H76" s="29">
+        <v>8</v>
+      </c>
+      <c r="I76" s="29">
+        <v>129</v>
+      </c>
+      <c r="J76" s="28">
+        <v>2015</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="77" spans="1:13">
-      <c r="A77" s="10" t="s">
-        <v>200</v>
-      </c>
-      <c r="B77" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="C77" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D77" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E77" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F77" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G77" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H77" s="29">
+      <c r="A77" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D77" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E77" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F77" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="H77" s="12">
         <v>10</v>
       </c>
-      <c r="I77" s="29">
-        <v>55</v>
-      </c>
-      <c r="J77" s="28">
-        <v>2021</v>
+      <c r="I77" s="12">
+        <v>23</v>
+      </c>
+      <c r="J77" s="35">
+        <v>2020</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="78" spans="1:13">
-      <c r="A78" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="B78" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D78" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E78" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F78" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G78" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="H78" s="46">
+      <c r="A78" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="B78" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="C78" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D78" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E78" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F78" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G78" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H78" s="29">
         <v>10</v>
       </c>
-      <c r="I78" s="46">
-        <v>11</v>
-      </c>
-      <c r="J78" s="48">
-        <v>2024</v>
+      <c r="I78" s="29">
+        <v>55</v>
+      </c>
+      <c r="J78" s="28">
+        <v>2021</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="M78" s="3"/>
+        <v>284</v>
+      </c>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="B79" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="C79" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D79" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E79" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F79" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G79" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H79" s="29">
+      <c r="A79" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B79" s="59" t="s">
+        <v>3</v>
+      </c>
+      <c r="C79" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D79" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E79" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F79" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G79" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="H79" s="46">
         <v>10</v>
       </c>
-      <c r="I79" s="29">
-        <v>58</v>
-      </c>
-      <c r="J79" s="28">
-        <v>2020</v>
+      <c r="I79" s="46">
+        <v>11</v>
+      </c>
+      <c r="J79" s="48">
+        <v>2024</v>
       </c>
       <c r="K79" s="5" t="s">
-        <v>296</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="M79" s="3"/>
     </row>
     <row r="80" spans="1:13">
-      <c r="A80" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="C80" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D80" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E80" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F80" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G80" s="23"/>
-      <c r="H80" s="12">
-        <v>8</v>
-      </c>
-      <c r="I80" s="12">
-        <v>50</v>
-      </c>
-      <c r="J80" s="35">
+      <c r="A80" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B80" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="C80" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D80" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F80" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G80" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H80" s="29">
+        <v>10</v>
+      </c>
+      <c r="I80" s="29">
+        <v>58</v>
+      </c>
+      <c r="J80" s="28">
         <v>2020</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="81" spans="1:12">
-      <c r="A81" s="55" t="s">
-        <v>78</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="C81" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D81" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E81" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F81" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G81" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H81" s="29">
-        <v>10</v>
-      </c>
-      <c r="I81" s="29">
-        <v>105</v>
-      </c>
-      <c r="J81" s="28">
-        <v>2022</v>
+      <c r="A81" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E81" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F81" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G81" s="23"/>
+      <c r="H81" s="12">
+        <v>8</v>
+      </c>
+      <c r="I81" s="12">
+        <v>50</v>
+      </c>
+      <c r="J81" s="35">
+        <v>2020</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>254</v>
+        <v>292</v>
       </c>
     </row>
     <row r="82" spans="1:12">
-      <c r="A82" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="B82" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C82" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D82" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E82" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F82" s="23"/>
-      <c r="G82" s="23"/>
-      <c r="H82" s="12">
-        <v>6</v>
-      </c>
-      <c r="I82" s="12">
-        <v>26</v>
-      </c>
-      <c r="J82" s="35">
-        <v>2018</v>
+      <c r="A82" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="B82" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C82" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D82" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E82" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F82" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G82" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H82" s="29">
+        <v>10</v>
+      </c>
+      <c r="I82" s="29">
+        <v>105</v>
+      </c>
+      <c r="J82" s="28">
+        <v>2022</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="83" spans="1:12">
-      <c r="A83" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="B83" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="C83" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D83" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E83" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F83" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G83" s="31"/>
-      <c r="H83" s="29">
-        <v>8</v>
-      </c>
-      <c r="I83" s="29">
-        <v>6500</v>
-      </c>
-      <c r="J83" s="28">
-        <v>2022</v>
+      <c r="A83" s="53" t="s">
+        <v>77</v>
+      </c>
+      <c r="B83" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F83" s="23"/>
+      <c r="G83" s="23"/>
+      <c r="H83" s="12">
+        <v>6</v>
+      </c>
+      <c r="I83" s="12">
+        <v>26</v>
+      </c>
+      <c r="J83" s="35">
+        <v>2018</v>
       </c>
       <c r="K83" s="5" t="s">
-        <v>295</v>
+        <v>228</v>
       </c>
     </row>
     <row r="84" spans="1:12">
-      <c r="A84" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="B84" s="20" t="s">
-        <v>115</v>
-      </c>
-      <c r="C84" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D84" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E84" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F84" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G84" s="23"/>
-      <c r="H84" s="12">
+      <c r="A84" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C84" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D84" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E84" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F84" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G84" s="31"/>
+      <c r="H84" s="29">
         <v>8</v>
       </c>
-      <c r="I84" s="12">
-        <v>108</v>
-      </c>
-      <c r="J84" s="35">
-        <v>2015</v>
+      <c r="I84" s="29">
+        <v>6500</v>
+      </c>
+      <c r="J84" s="28">
+        <v>2022</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:12">
-      <c r="A85" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="B85" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C85" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D85" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E85" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F85" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G85" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H85" s="29">
-        <v>10</v>
-      </c>
-      <c r="I85" s="29">
-        <v>84</v>
-      </c>
-      <c r="J85" s="28">
+      <c r="A85" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="B85" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E85" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G85" s="23"/>
+      <c r="H85" s="12">
+        <v>8</v>
+      </c>
+      <c r="I85" s="12">
+        <v>108</v>
+      </c>
+      <c r="J85" s="35">
         <v>2015</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="L85" s="4" t="s">
-        <v>207</v>
+        <v>285</v>
       </c>
     </row>
     <row r="86" spans="1:12">
-      <c r="A86" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="B86" s="20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C86" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D86" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E86" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F86" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G86" s="23"/>
-      <c r="H86" s="12">
-        <v>8</v>
-      </c>
-      <c r="I86" s="12">
-        <v>140</v>
-      </c>
-      <c r="J86" s="35">
-        <v>2020</v>
+      <c r="A86" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C86" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D86" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E86" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F86" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G86" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H86" s="29">
+        <v>10</v>
+      </c>
+      <c r="I86" s="29">
+        <v>84</v>
+      </c>
+      <c r="J86" s="28">
+        <v>2015</v>
       </c>
       <c r="K86" s="5" t="s">
-        <v>286</v>
+        <v>212</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="87" spans="1:12">
-      <c r="A87" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B87" s="60" t="s">
-        <v>18</v>
-      </c>
-      <c r="C87" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="D87" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="E87" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F87" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="G87" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="H87" s="42">
-        <v>10</v>
-      </c>
-      <c r="I87" s="42">
-        <v>17</v>
-      </c>
-      <c r="J87" s="44">
-        <v>2024</v>
+      <c r="A87" s="53" t="s">
+        <v>106</v>
+      </c>
+      <c r="B87" s="20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G87" s="23"/>
+      <c r="H87" s="12">
+        <v>8</v>
+      </c>
+      <c r="I87" s="12">
+        <v>140</v>
+      </c>
+      <c r="J87" s="35">
+        <v>2020</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
     </row>
     <row r="88" spans="1:12">
-      <c r="A88" s="53" t="s">
-        <v>107</v>
-      </c>
-      <c r="B88" s="20" t="s">
-        <v>117</v>
-      </c>
-      <c r="C88" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D88" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E88" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F88" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G88" s="23"/>
-      <c r="H88" s="12">
-        <v>8</v>
-      </c>
-      <c r="I88" s="12">
-        <v>35</v>
-      </c>
-      <c r="J88" s="35">
-        <v>2022</v>
+      <c r="A88" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B88" s="60" t="s">
+        <v>18</v>
+      </c>
+      <c r="C88" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="D88" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="E88" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F88" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G88" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="H88" s="42">
+        <v>10</v>
+      </c>
+      <c r="I88" s="42">
+        <v>17</v>
+      </c>
+      <c r="J88" s="44">
+        <v>2024</v>
       </c>
       <c r="K88" s="5" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
     </row>
     <row r="89" spans="1:12">
-      <c r="A89" s="32" t="s">
-        <v>204</v>
-      </c>
-      <c r="B89" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="C89" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="D89" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="E89" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="F89" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="G89" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="H89" s="29">
-        <v>10</v>
-      </c>
-      <c r="I89" s="29">
-        <v>24</v>
-      </c>
-      <c r="J89" s="28">
-        <v>2021</v>
+      <c r="A89" s="53" t="s">
+        <v>107</v>
+      </c>
+      <c r="B89" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F89" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G89" s="23"/>
+      <c r="H89" s="12">
+        <v>8</v>
+      </c>
+      <c r="I89" s="12">
+        <v>35</v>
+      </c>
+      <c r="J89" s="35">
+        <v>2022</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>241</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90" spans="1:12">
-      <c r="A90" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="B90" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C90" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="D90" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="F90" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G90" s="23"/>
-      <c r="H90" s="12">
-        <v>8</v>
-      </c>
-      <c r="I90" s="12">
-        <v>21</v>
-      </c>
-      <c r="J90" s="35">
-        <v>2020</v>
+      <c r="A90" s="32" t="s">
+        <v>204</v>
+      </c>
+      <c r="B90" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="C90" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="D90" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="E90" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="F90" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="G90" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="H90" s="29">
+        <v>10</v>
+      </c>
+      <c r="I90" s="29">
+        <v>24</v>
+      </c>
+      <c r="J90" s="28">
+        <v>2021</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>215</v>
+        <v>241</v>
       </c>
     </row>
     <row r="91" spans="1:12">
-      <c r="A91" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="B91" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="C91" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D91" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="E91" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F91" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G91" s="65"/>
-      <c r="H91" s="42">
+      <c r="A91" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="B91" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="D91" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="E91" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="F91" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G91" s="23"/>
+      <c r="H91" s="12">
         <v>8</v>
       </c>
-      <c r="I91" s="42">
-        <v>73</v>
-      </c>
-      <c r="J91" s="44">
-        <v>2025</v>
+      <c r="I91" s="12">
+        <v>21</v>
+      </c>
+      <c r="J91" s="35">
+        <v>2020</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>268</v>
+        <v>215</v>
       </c>
     </row>
     <row r="92" spans="1:12">
-      <c r="A92" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B92" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="C92" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D92" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E92" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F92" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G92" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="H92" s="46">
-        <v>10</v>
-      </c>
-      <c r="I92" s="46">
-        <v>43</v>
-      </c>
-      <c r="J92" s="48">
+      <c r="A92" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B92" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D92" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="E92" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F92" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="G92" s="65"/>
+      <c r="H92" s="42">
+        <v>8</v>
+      </c>
+      <c r="I92" s="42">
+        <v>73</v>
+      </c>
+      <c r="J92" s="44">
         <v>2025</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="93" spans="1:12">
-      <c r="A93" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="B93" s="60" t="s">
-        <v>19</v>
-      </c>
-      <c r="C93" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="D93" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="E93" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="F93" s="64" t="s">
-        <v>118</v>
-      </c>
-      <c r="G93" s="64"/>
-      <c r="H93" s="42">
-        <v>8</v>
-      </c>
-      <c r="I93" s="42">
-        <v>38</v>
-      </c>
-      <c r="J93" s="44">
+      <c r="A93" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="B93" s="59" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D93" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E93" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F93" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G93" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="H93" s="46">
+        <v>10</v>
+      </c>
+      <c r="I93" s="46">
+        <v>43</v>
+      </c>
+      <c r="J93" s="48">
         <v>2025</v>
       </c>
       <c r="K93" s="5" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:12">
-      <c r="A94" s="24" t="s">
-        <v>48</v>
-      </c>
-      <c r="B94" s="59" t="s">
-        <v>15</v>
-      </c>
-      <c r="C94" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="D94" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="E94" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="F94" s="63" t="s">
-        <v>118</v>
-      </c>
-      <c r="G94" s="63"/>
-      <c r="H94" s="46">
+      <c r="A94" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B94" s="60" t="s">
+        <v>19</v>
+      </c>
+      <c r="C94" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="D94" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="E94" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="F94" s="64" t="s">
+        <v>118</v>
+      </c>
+      <c r="G94" s="64"/>
+      <c r="H94" s="42">
         <v>8</v>
       </c>
-      <c r="I94" s="46">
-        <v>18</v>
-      </c>
-      <c r="J94" s="48">
+      <c r="I94" s="42">
+        <v>38</v>
+      </c>
+      <c r="J94" s="44">
         <v>2025</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
     </row>
     <row r="95" spans="1:12">
-      <c r="A95" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="B95" s="60" t="s">
-        <v>22</v>
-      </c>
-      <c r="C95" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D95" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="E95" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F95" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G95" s="65"/>
-      <c r="H95" s="42">
+      <c r="A95" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="B95" s="59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="D95" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="E95" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="F95" s="63" t="s">
+        <v>118</v>
+      </c>
+      <c r="G95" s="63"/>
+      <c r="H95" s="46">
         <v>8</v>
       </c>
-      <c r="I95" s="42">
-        <v>40</v>
-      </c>
-      <c r="J95" s="44">
-        <v>2024</v>
+      <c r="I95" s="46">
+        <v>18</v>
+      </c>
+      <c r="J95" s="48">
+        <v>2025</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
     </row>
     <row r="96" spans="1:12">
-      <c r="A96" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B96" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="C96" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D96" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E96" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F96" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G96" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="H96" s="46">
-        <v>10</v>
-      </c>
-      <c r="I96" s="46">
-        <v>25</v>
-      </c>
-      <c r="J96" s="48">
-        <v>2025</v>
+      <c r="A96" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B96" s="60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C96" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D96" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="E96" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F96" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="G96" s="65"/>
+      <c r="H96" s="42">
+        <v>8</v>
+      </c>
+      <c r="I96" s="42">
+        <v>40</v>
+      </c>
+      <c r="J96" s="44">
+        <v>2024</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="97" spans="1:11">
-      <c r="A97" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="B97" s="60" t="s">
+      <c r="A97" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="B97" s="59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C97" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D97" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F97" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G97" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="H97" s="46">
+        <v>10</v>
+      </c>
+      <c r="I97" s="46">
         <v>25</v>
       </c>
-      <c r="C97" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D97" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="E97" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F97" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G97" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="H97" s="42">
-        <v>10</v>
-      </c>
-      <c r="I97" s="42">
-        <v>99</v>
-      </c>
-      <c r="J97" s="44">
-        <v>2024</v>
+      <c r="J97" s="48">
+        <v>2025</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="98" spans="1:11">
-      <c r="A98" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B98" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="C98" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D98" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E98" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F98" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G98" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="H98" s="46">
+      <c r="A98" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B98" s="60" t="s">
+        <v>25</v>
+      </c>
+      <c r="C98" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D98" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="E98" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F98" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="G98" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="H98" s="42">
         <v>10</v>
       </c>
-      <c r="I98" s="46">
-        <v>46</v>
-      </c>
-      <c r="J98" s="48">
+      <c r="I98" s="42">
+        <v>99</v>
+      </c>
+      <c r="J98" s="44">
         <v>2024</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
     </row>
     <row r="99" spans="1:11">
-      <c r="A99" s="32" t="s">
+      <c r="A99" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="B99" s="59" t="s">
+        <v>8</v>
+      </c>
+      <c r="C99" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D99" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E99" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F99" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G99" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="H99" s="46">
+        <v>10</v>
+      </c>
+      <c r="I99" s="46">
+        <v>46</v>
+      </c>
+      <c r="J99" s="48">
+        <v>2024</v>
+      </c>
+      <c r="K99" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="B99" s="60" t="s">
+      <c r="B100" s="60" t="s">
         <v>20</v>
       </c>
-      <c r="C99" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="D99" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="E99" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="F99" s="65" t="s">
-        <v>118</v>
-      </c>
-      <c r="G99" s="65"/>
-      <c r="H99" s="42">
+      <c r="C100" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D100" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="E100" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="F100" s="65" t="s">
+        <v>118</v>
+      </c>
+      <c r="G100" s="65"/>
+      <c r="H100" s="42">
         <v>8</v>
       </c>
-      <c r="I99" s="42">
+      <c r="I100" s="42">
         <v>202</v>
       </c>
-      <c r="J99" s="44">
+      <c r="J100" s="44">
         <v>2025</v>
       </c>
-      <c r="K99" s="5" t="s">
+      <c r="K100" s="5" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A100" s="24" t="s">
+    <row r="101" spans="1:11" ht="15.75" thickBot="1">
+      <c r="A101" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="B100" s="59" t="s">
+      <c r="B101" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="C100" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D100" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="E100" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="F100" s="47" t="s">
-        <v>118</v>
-      </c>
-      <c r="G100" s="47"/>
-      <c r="H100" s="46">
+      <c r="C101" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="D101" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="E101" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="F101" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="G101" s="47"/>
+      <c r="H101" s="46">
         <v>8</v>
       </c>
-      <c r="I100" s="46">
+      <c r="I101" s="46">
         <v>52</v>
       </c>
-      <c r="J100" s="48">
+      <c r="J101" s="48">
         <v>2025</v>
       </c>
-      <c r="K100" s="5" t="s">
+      <c r="K101" s="5" t="s">
         <v>271</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" s="6" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A101" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B101" s="57" t="s">
-        <v>26</v>
-      </c>
-      <c r="C101" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D101" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="E101" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="F101" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="G101" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="H101" s="39">
-        <v>10</v>
-      </c>
-      <c r="I101" s="39">
-        <v>83</v>
-      </c>
-      <c r="J101" s="41">
-        <v>2024</v>
-      </c>
-      <c r="K101" s="5" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="6" customFormat="1" ht="15.75" thickBot="1">
-      <c r="A102" s="35" t="s">
+      <c r="A102" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B102" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C102" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="D102" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="E102" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="F102" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="G102" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="H102" s="39">
+        <v>10</v>
+      </c>
+      <c r="I102" s="39">
+        <v>83</v>
+      </c>
+      <c r="J102" s="41">
+        <v>2024</v>
+      </c>
+      <c r="K102" s="5" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" s="6" customFormat="1" ht="15.75" thickBot="1">
+      <c r="A103" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="B102" s="56" t="s">
+      <c r="B103" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="C102" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="D102" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E102" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="F102" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="G102" s="37"/>
-      <c r="H102" s="36">
+      <c r="C103" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="D103" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="F103" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="G103" s="37"/>
+      <c r="H103" s="36">
         <v>8</v>
       </c>
-      <c r="I102" s="36">
+      <c r="I103" s="36">
         <v>66</v>
       </c>
-      <c r="J102" s="38">
+      <c r="J103" s="38">
         <v>2025</v>
       </c>
-      <c r="K102" s="5" t="s">
+      <c r="K103" s="5" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="103" spans="1:11">
-      <c r="B103" s="6"/>
-      <c r="C103" s="6"/>
-      <c r="D103" s="6"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
     </row>
     <row r="104" spans="1:11">
       <c r="B104" s="6"/>
@@ -12184,12 +12197,23 @@
       <c r="D106" s="6"/>
       <c r="E106" s="6"/>
       <c r="F106" s="6"/>
-      <c r="G106" s="7"/>
+      <c r="G106" s="6"/>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="B107" s="6"/>
+      <c r="C107" s="6"/>
+      <c r="D107" s="6"/>
+      <c r="E107" s="6"/>
+      <c r="F107" s="6"/>
+      <c r="G107" s="7"/>
     </row>
   </sheetData>
   <sortState ref="A1:N108">
     <sortCondition ref="A1"/>
   </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Extraction Table.xlsx
+++ b/Extraction Table.xlsx
@@ -5126,74 +5126,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">(Coding, design, metamodeling, V&amp;V), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Artifacts</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">(languages, tools, models, transformation, proccess/approaches, Patterns), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Domain</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>(Automotion))</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8" tint="-0.249977111117893"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Phase</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>(Coding</t>
     </r>
     <r>
@@ -8018,6 +7950,74 @@
   </si>
   <si>
     <t>Article title: Model-Driven Development: A Tertiary Review - Journal: Sosym - author names: Raoni Sales de Oliveira, Ana Patrícia Fontes Magalhães Mascarenhas, Rita Suzana Pitangueira Maciel - Affiliation: Universidade Federal da Bahia - e-mail: raoni_si@hotmail.com</t>
+  </si>
+  <si>
+    <r>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Phase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(Coding, design, metamodeling, V&amp;V), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Artifacts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(languages, tools, models, transformation, proccess/approaches, Patterns), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8" tint="-0.249977111117893"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Domain</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(MDD for AI))</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -8728,7 +8728,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="73" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B1" s="73"/>
       <c r="C1" s="73"/>
@@ -8743,37 +8743,37 @@
     </row>
     <row r="2" spans="1:11" ht="15.75" thickBot="1">
       <c r="A2" s="69" t="s">
+        <v>301</v>
+      </c>
+      <c r="B2" s="69" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2" s="70" t="s">
         <v>302</v>
       </c>
-      <c r="B2" s="69" t="s">
-        <v>312</v>
-      </c>
-      <c r="C2" s="70" t="s">
+      <c r="D2" s="70" t="s">
         <v>303</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="E2" s="70" t="s">
         <v>304</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="F2" s="70" t="s">
         <v>305</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="G2" s="70" t="s">
         <v>306</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="H2" s="70" t="s">
         <v>307</v>
       </c>
-      <c r="H2" s="70" t="s">
+      <c r="I2" s="70" t="s">
+        <v>310</v>
+      </c>
+      <c r="J2" s="70" t="s">
         <v>308</v>
       </c>
-      <c r="I2" s="70" t="s">
-        <v>311</v>
-      </c>
-      <c r="J2" s="70" t="s">
+      <c r="K2" s="68" t="s">
         <v>309</v>
-      </c>
-      <c r="K2" s="68" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1">
@@ -9374,7 +9374,7 @@
         <v>2022</v>
       </c>
       <c r="K20" s="71" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="15.75" thickBot="1">
@@ -9405,7 +9405,7 @@
         <v>2015</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="15.75" thickBot="1">
@@ -9675,7 +9675,7 @@
         <v>2015</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -9811,7 +9811,7 @@
         <v>2022</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -9842,7 +9842,7 @@
         <v>2018</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -9941,7 +9941,7 @@
         <v>2022</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -9974,7 +9974,7 @@
         <v>2022</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -10007,7 +10007,7 @@
         <v>2021</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="40" spans="1:12">
@@ -10038,7 +10038,7 @@
         <v>2019</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="41" spans="1:12">
@@ -10170,7 +10170,7 @@
         <v>2023</v>
       </c>
       <c r="K44" s="13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -10302,7 +10302,7 @@
         <v>2018</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>206</v>
@@ -10338,7 +10338,7 @@
         <v>2023</v>
       </c>
       <c r="K49" s="71" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -10373,7 +10373,7 @@
         <v>2025</v>
       </c>
       <c r="K50" s="14" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -10472,7 +10472,7 @@
         <v>2019</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -10575,7 +10575,7 @@
         <v>2016</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -10806,7 +10806,7 @@
         <v>2022</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -10874,7 +10874,7 @@
         <v>2023</v>
       </c>
       <c r="K65" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="66" spans="1:13">
@@ -11046,7 +11046,7 @@
         <v>2023</v>
       </c>
       <c r="K70" s="71" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="71" spans="1:13">
@@ -11114,7 +11114,7 @@
         <v>2023</v>
       </c>
       <c r="K72" s="72" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="L72" s="1" t="s">
         <v>44</v>
@@ -11253,7 +11253,7 @@
         <v>2015</v>
       </c>
       <c r="K76" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="77" spans="1:13">
@@ -11288,7 +11288,7 @@
         <v>2020</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="78" spans="1:13">
@@ -11323,7 +11323,7 @@
         <v>2021</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="79" spans="1:13">
@@ -11394,7 +11394,7 @@
         <v>2020</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -11427,7 +11427,7 @@
         <v>2020</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -11526,7 +11526,7 @@
         <v>2022</v>
       </c>
       <c r="K84" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -11559,7 +11559,7 @@
         <v>2015</v>
       </c>
       <c r="K85" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -11630,7 +11630,7 @@
         <v>2020</v>
       </c>
       <c r="K87" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -11698,7 +11698,7 @@
         <v>2022</v>
       </c>
       <c r="K89" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -11867,7 +11867,7 @@
         <v>2025</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -11900,7 +11900,7 @@
         <v>2025</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>270</v>
+        <v>317</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -11933,7 +11933,7 @@
         <v>2024</v>
       </c>
       <c r="K96" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -11968,7 +11968,7 @@
         <v>2025</v>
       </c>
       <c r="K97" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -12003,7 +12003,7 @@
         <v>2024</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -12038,7 +12038,7 @@
         <v>2024</v>
       </c>
       <c r="K99" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -12071,7 +12071,7 @@
         <v>2025</v>
       </c>
       <c r="K100" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="15.75" thickBot="1">
@@ -12104,7 +12104,7 @@
         <v>2025</v>
       </c>
       <c r="K101" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:11" s="6" customFormat="1" ht="15.75" thickBot="1">
